--- a/Result/profitability/4716.xlsx
+++ b/Result/profitability/4716.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>-0.11</v>
       </c>
       <c r="N2" t="n">
-        <v>10.2425</v>
+        <v>11.68</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.095</v>
+        <v>-0.08374999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>10.755</v>
+        <v>11.9425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05499999999999999</v>
+        <v>-0.01249999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.44125</v>
+        <v>12.39125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1020,10 +1020,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.009999999999999993</v>
+        <v>0.11125</v>
       </c>
       <c r="N5" t="n">
-        <v>11.92875</v>
+        <v>13.11625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1175</v>
+        <v>0.0475</v>
       </c>
       <c r="N6" t="n">
-        <v>12.96</v>
+        <v>14.28125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0775</v>
+        <v>0.08125</v>
       </c>
       <c r="N7" t="n">
-        <v>14.26875</v>
+        <v>14.795</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1283,13 +1283,13 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1075</v>
+        <v>0.08249999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>14.99125</v>
+        <v>15.46</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4716</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>131</v>
+      </c>
+      <c r="D75" t="n">
+        <v>107</v>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-11.62%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.11375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.01125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.176470588235294</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2615062761506277</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.10593713620489</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
